--- a/public/downloads/TaskListSampleData.xlsx
+++ b/public/downloads/TaskListSampleData.xlsx
@@ -19,13 +19,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -432,52 +436,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>RAG</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Project lead</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Start date</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Estimated end</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Next milestone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Obstacles</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -507,10 +511,10 @@
       <c r="E2" t="n">
         <v>72</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="2" t="n">
         <v>46184</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <v>46284</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -549,10 +553,10 @@
       <c r="E3" t="n">
         <v>45</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <v>46264</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -595,10 +599,10 @@
       <c r="E4" t="n">
         <v>18</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="2" t="n">
         <v>46214</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="2" t="n">
         <v>46254</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -625,7 +629,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>On track</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -641,10 +645,10 @@
       <c r="E5" t="n">
         <v>88</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>46259</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -653,7 +657,11 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Near release</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -663,7 +671,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>At risk</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -679,10 +687,10 @@
       <c r="E6" t="n">
         <v>55</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="2" t="n">
         <v>46044</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>46249</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -705,7 +713,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -721,10 +729,10 @@
       <c r="E7" t="n">
         <v>12</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="2" t="n">
         <v>46249</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="2" t="n">
         <v>46424</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -747,7 +755,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -763,10 +771,10 @@
       <c r="E8" t="n">
         <v>100</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="2" t="n">
         <v>45844</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="H8" t="inlineStr">
@@ -789,7 +797,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -805,10 +813,10 @@
       <c r="E9" t="n">
         <v>33</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="2" t="n">
         <v>46199</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="H9" t="inlineStr">

--- a/public/downloads/TaskListSampleData.xlsx
+++ b/public/downloads/TaskListSampleData.xlsx
@@ -19,16 +19,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -51,9 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -436,52 +432,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>RAG</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Project lead</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Start date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Estimated end</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Next milestone</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Obstacles</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -511,10 +507,10 @@
       <c r="E2" t="n">
         <v>72</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>46184</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>46284</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,10 +549,10 @@
       <c r="E3" t="n">
         <v>45</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>46264</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -599,10 +595,10 @@
       <c r="E4" t="n">
         <v>18</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>46214</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>46254</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -629,7 +625,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>On track</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -645,10 +641,10 @@
       <c r="E5" t="n">
         <v>88</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>46124</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>46259</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -657,11 +653,7 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Near release</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -671,7 +663,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>At risk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -687,10 +679,10 @@
       <c r="E6" t="n">
         <v>55</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>46044</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>46249</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -713,7 +705,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -729,10 +721,10 @@
       <c r="E7" t="n">
         <v>12</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>46249</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>46424</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -755,7 +747,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -771,10 +763,10 @@
       <c r="E8" t="n">
         <v>100</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="1" t="n">
         <v>45844</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H8" t="inlineStr">
@@ -797,7 +789,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -813,10 +805,10 @@
       <c r="E9" t="n">
         <v>33</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="1" t="n">
         <v>46199</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="1" t="n">
         <v>46334</v>
       </c>
       <c r="H9" t="inlineStr">

--- a/public/downloads/TaskListSampleData.xlsx
+++ b/public/downloads/TaskListSampleData.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="How to use" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +20,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -425,59 +430,59 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>RAG</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Project lead</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Start date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Estimated end</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Next milestone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Obstacles</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -507,10 +512,10 @@
       <c r="E2" t="n">
         <v>72</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="2" t="n">
         <v>46184</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <v>46284</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -549,10 +554,10 @@
       <c r="E3" t="n">
         <v>45</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <v>46264</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -595,10 +600,10 @@
       <c r="E4" t="n">
         <v>18</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="2" t="n">
         <v>46214</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="2" t="n">
         <v>46254</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -625,7 +630,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>On track</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -641,10 +646,10 @@
       <c r="E5" t="n">
         <v>88</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>46259</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -653,7 +658,11 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Near release</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -663,7 +672,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>At risk</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -679,10 +688,10 @@
       <c r="E6" t="n">
         <v>55</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="2" t="n">
         <v>46044</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>46249</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -705,7 +714,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -721,10 +730,10 @@
       <c r="E7" t="n">
         <v>12</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="2" t="n">
         <v>46249</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="2" t="n">
         <v>46424</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -747,7 +756,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -763,10 +772,10 @@
       <c r="E8" t="n">
         <v>100</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="2" t="n">
         <v>45844</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="H8" t="inlineStr">
@@ -789,7 +798,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -805,10 +814,10 @@
       <c r="E9" t="n">
         <v>33</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="2" t="n">
         <v>46199</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="H9" t="inlineStr">
@@ -822,6 +831,102 @@
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="87" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Power BI Desktop test data for DataLund Task List</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Columns use the same suite field names as Gantt and Resource Load</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>(Project = Task well, Project lead = Resource well, RAG = status well).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1. Home → Get data → Excel workbook → select this file → load Projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2. Import taskList.pbiviz (Visualizations … → Import a visual from a file).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3. Bind: Project → Project, RAG → RAG, Group → Group, Project lead → Project lead,</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Progress → Progress, Start Date → Start Date, End Date → End Date,</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tooltips → Next milestone, Obstacles, Notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Progress is 0–100. RAG accepts Red / Amber / Green and Rød / Gul / Grønn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>For the full suite (Gantt + Resource Load on one page), use DatalundSuiteSample.xlsx.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/downloads/TaskListSampleData.xlsx
+++ b/public/downloads/TaskListSampleData.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Projects" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -160,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -172,7 +172,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -557,14 +556,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="88" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="82" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -576,18 +574,16 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Starter projects for the portfolio list</t>
+          <t>Core project columns only — swap in your own rows</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -604,65 +600,30 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Visualizations … → Import a visual from a file.</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2. Load Projects</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2. Load the Projects sheet from this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>3. Bind</t>
-        </is>
-      </c>
-    </row>
+          <t>3. Bind Project, RAG, Group, Project lead, Progress, Start Date, End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Project → Project · RAG → RAG · Group → Group · Project lead → Project lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Progress → Progress · Start Date → Start Date · End Date → End Date</t>
-        </is>
-      </c>
-    </row>
+          <t>Project = Task well · Project lead = Resource well. Full suite → DatalundSuiteSample.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Tooltips → Next milestone, Obstacles, Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Project = Task well · Project lead = Resource well · RAG = status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Want Gantt + Resource Load on the same page? Use DatalundSuiteSample.xlsx.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>https://datalund.no/visuals/task-list/</t>
         </is>
@@ -670,11 +631,11 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -687,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -697,283 +658,202 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>RAG</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Project lead</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>Next milestone</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>Obstacles</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>North Sea Hub</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Delivery</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Ada Ng</t>
         </is>
       </c>
-      <c r="E2" s="13" t="n">
+      <c r="E2" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="F2" s="14" t="n">
+      <c r="F2" s="13" t="n">
         <v>46184</v>
       </c>
-      <c r="G2" s="14" t="n">
+      <c r="G2" s="13" t="n">
         <v>46284</v>
       </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t>FAT complete</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr"/>
-      <c r="J2" s="11" t="inlineStr">
-        <is>
-          <t>On track for Q3</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Arctic Link</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Amber</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Delivery</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Bo Berg</t>
         </is>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="17" t="n">
         <v>46154</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="17" t="n">
         <v>46264</v>
       </c>
-      <c r="H3" s="15" t="inlineStr">
-        <is>
-          <t>Cable pull</t>
-        </is>
-      </c>
-      <c r="I3" s="15" t="inlineStr">
-        <is>
-          <t>Weather window</t>
-        </is>
-      </c>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>Watch supplier lead time</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Yard Retrofit</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Initiation</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Cara Diaz</t>
         </is>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="13" t="n">
         <v>46214</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="13" t="n">
         <v>46254</v>
       </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>Scope freeze</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Budget overrun</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>Critical path slip</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Digital Twin v2</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Dan Okonkwo</t>
         </is>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="17" t="n">
         <v>46124</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="17" t="n">
         <v>46259</v>
       </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>UAT</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr"/>
-      <c r="J5" s="15" t="inlineStr">
-        <is>
-          <t>Near release</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Port Expansion</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Amber</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Finn Olsen</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="13" t="n">
         <v>46249</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="13" t="n">
         <v>46424</v>
       </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>Permits</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>Replace these rows with your projects</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J6"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/TaskListSampleData.xlsx
+++ b/public/downloads/TaskListSampleData.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Projects" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$F$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="82" customWidth="1" min="1" max="1"/>
@@ -578,7 +578,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Core project columns only — swap in your own rows</t>
+          <t>Portfolio columns only — swap in your own rows</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -609,7 +609,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>3. Bind Project, RAG, Group, Project lead, Progress, Start Date, End Date</t>
+          <t>3. Bind Project, RAG, Project lead, Progress, Start Date, End Date</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,20 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Project = Task well · Project lead = Resource well. Full suite → DatalundSuiteSample.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+          <t>Project = Task well · Project lead = Resource well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Group is optional later (phase sections). Full suite → DatalundSuiteSample.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>https://datalund.no/visuals/task-list/</t>
         </is>
@@ -635,7 +642,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -648,16 +655,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -673,25 +679,20 @@
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Project lead</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>Project lead</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
@@ -710,21 +711,16 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
           <t>Ada Ng</t>
         </is>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="D2" s="12" t="n">
         <v>72</v>
       </c>
+      <c r="E2" s="13" t="n">
+        <v>46184</v>
+      </c>
       <c r="F2" s="13" t="n">
-        <v>46184</v>
-      </c>
-      <c r="G2" s="13" t="n">
         <v>46284</v>
       </c>
     </row>
@@ -741,21 +737,16 @@
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
           <t>Bo Berg</t>
         </is>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="16" t="n">
         <v>45</v>
       </c>
+      <c r="E3" s="17" t="n">
+        <v>46154</v>
+      </c>
       <c r="F3" s="17" t="n">
-        <v>46154</v>
-      </c>
-      <c r="G3" s="17" t="n">
         <v>46264</v>
       </c>
     </row>
@@ -772,21 +763,16 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Initiation</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
           <t>Cara Diaz</t>
         </is>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="D4" s="12" t="n">
         <v>18</v>
       </c>
+      <c r="E4" s="13" t="n">
+        <v>46214</v>
+      </c>
       <c r="F4" s="13" t="n">
-        <v>46214</v>
-      </c>
-      <c r="G4" s="13" t="n">
         <v>46254</v>
       </c>
     </row>
@@ -803,21 +789,16 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
           <t>Dan Okonkwo</t>
         </is>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="16" t="n">
         <v>88</v>
       </c>
+      <c r="E5" s="17" t="n">
+        <v>46124</v>
+      </c>
       <c r="F5" s="17" t="n">
-        <v>46124</v>
-      </c>
-      <c r="G5" s="17" t="n">
         <v>46259</v>
       </c>
     </row>
@@ -834,26 +815,21 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
           <t>Finn Olsen</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="D6" s="12" t="n">
         <v>12</v>
       </c>
+      <c r="E6" s="13" t="n">
+        <v>46249</v>
+      </c>
       <c r="F6" s="13" t="n">
-        <v>46249</v>
-      </c>
-      <c r="G6" s="13" t="n">
         <v>46424</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/TaskListSampleData.xlsx
+++ b/public/downloads/TaskListSampleData.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Projects" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="82" customWidth="1" min="1" max="1"/>
@@ -578,7 +578,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Portfolio columns only — swap in your own rows</t>
+          <t>Core project columns only — swap in your own rows</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -609,7 +609,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>3. Bind Project, RAG, Project lead, Progress, Start Date, End Date</t>
+          <t>3. Bind Project, RAG, Group, Project lead, Progress, Start Date, End Date</t>
         </is>
       </c>
     </row>
@@ -617,20 +617,13 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Project = Task well · Project lead = Resource well.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Group is optional later (phase sections). Full suite → DatalundSuiteSample.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+          <t>Project = Task well · Project lead = Resource well. Full suite → DatalundSuiteSample.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>https://datalund.no/visuals/task-list/</t>
         </is>
@@ -642,7 +635,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -655,15 +648,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -679,20 +673,25 @@
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
           <t>Project lead</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
@@ -711,16 +710,21 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
           <t>Ada Ng</t>
         </is>
       </c>
-      <c r="D2" s="12" t="n">
+      <c r="E2" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="E2" s="13" t="n">
+      <c r="F2" s="13" t="n">
         <v>46184</v>
       </c>
-      <c r="F2" s="13" t="n">
+      <c r="G2" s="13" t="n">
         <v>46284</v>
       </c>
     </row>
@@ -737,16 +741,21 @@
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
           <t>Bo Berg</t>
         </is>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="E3" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="F3" s="17" t="n">
         <v>46154</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="G3" s="17" t="n">
         <v>46264</v>
       </c>
     </row>
@@ -763,16 +772,21 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
+          <t>Initiation</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
           <t>Cara Diaz</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="E4" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="F4" s="13" t="n">
         <v>46214</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="G4" s="13" t="n">
         <v>46254</v>
       </c>
     </row>
@@ -789,16 +803,21 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
           <t>Dan Okonkwo</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="E5" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="F5" s="17" t="n">
         <v>46124</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="G5" s="17" t="n">
         <v>46259</v>
       </c>
     </row>
@@ -815,21 +834,26 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
           <t>Finn Olsen</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="F6" s="13" t="n">
         <v>46249</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="G6" s="13" t="n">
         <v>46424</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>